--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS382 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70EDAC2C-CDD7-4742-8539-9117B253CC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD25086B-640A-EB43-8646-4E33B2E7F9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2280" yWindow="7940" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Week</t>
   </si>
@@ -189,6 +189,12 @@
   </si>
   <si>
     <t>Introduction to Predictive Modeling</t>
+  </si>
+  <si>
+    <t>01-Linear_Regression</t>
+  </si>
+  <si>
+    <t>2K6OQ35rk5c</t>
   </si>
 </sst>
 </file>
@@ -1164,6 +1170,12 @@
       <c r="G3" t="s">
         <v>21</v>
       </c>
+      <c r="H3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS382 2026 Fall/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/IS382 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD25086B-640A-EB43-8646-4E33B2E7F9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AE587F-5F69-CF49-B362-A858F8046545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="7940" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Week</t>
   </si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t>2K6OQ35rk5c</t>
+  </si>
+  <si>
+    <t>02-Multiple_Regression</t>
+  </si>
+  <si>
+    <t>4a3B1VUZ0Ik</t>
   </si>
 </sst>
 </file>
@@ -1074,12 +1080,13 @@
   <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="17.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="38.83203125" customWidth="1"/>
-    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -1202,6 +1209,12 @@
       <c r="G4" t="s">
         <v>22</v>
       </c>
+      <c r="H4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/IS382 2026 Fall/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS382 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AE587F-5F69-CF49-B362-A858F8046545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202F16E8-0766-FF4C-A964-31739863009D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
+    <workbookView xWindow="2780" yWindow="8060" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Week</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t>4a3B1VUZ0Ik</t>
+  </si>
+  <si>
+    <t>03-Logistic_Regression</t>
+  </si>
+  <si>
+    <t>Wd6E7sxzJMQ</t>
   </si>
 </sst>
 </file>
@@ -1241,6 +1247,12 @@
       <c r="G5" t="s">
         <v>23</v>
       </c>
+      <c r="H5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS382 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202F16E8-0766-FF4C-A964-31739863009D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F48860-1C43-A540-BEB0-0D99543B70DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="8060" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
+    <workbookView xWindow="920" yWindow="5100" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -95,39 +95,6 @@
     <t>Topic</t>
   </si>
   <si>
-    <t>/assignments/statistical_learning.Rmd</t>
-  </si>
-  <si>
-    <t>/assignments/linear_regression.Rmd</t>
-  </si>
-  <si>
-    <t>/assignments/multiple_regression.Rmd</t>
-  </si>
-  <si>
-    <t>/assignments/logistic_regression.Rmd</t>
-  </si>
-  <si>
-    <t>/assignments/classification.Rmd</t>
-  </si>
-  <si>
-    <t>/assignments/resampling_methods.Rmd</t>
-  </si>
-  <si>
-    <t>/assignments/decision_trees.Rmd</t>
-  </si>
-  <si>
-    <t>/assignments/bagging_and_random_forests.Rmd</t>
-  </si>
-  <si>
-    <t>/assignments/support_vector_machines.Rmd</t>
-  </si>
-  <si>
-    <t>/assignments/principal_component_analysis.Rmd</t>
-  </si>
-  <si>
-    <t>/assignments/clustering.Rmd</t>
-  </si>
-  <si>
     <t>No Meetup - Thanksgiving</t>
   </si>
   <si>
@@ -207,6 +174,39 @@
   </si>
   <si>
     <t>Wd6E7sxzJMQ</t>
+  </si>
+  <si>
+    <t>/assignments/classification/classification.Rmd</t>
+  </si>
+  <si>
+    <t>/assignments/statistical_learning/statistical_learning.Rmd</t>
+  </si>
+  <si>
+    <t>/assignments/linear_regression/linear_regression.Rmd</t>
+  </si>
+  <si>
+    <t>/assignments/multiple_regression/multiple_regression.Rmd</t>
+  </si>
+  <si>
+    <t>/assignments/logistic_regression/logistic_regression.Rmd</t>
+  </si>
+  <si>
+    <t>/assignments/resampling_methods/resampling_methods.Rmd</t>
+  </si>
+  <si>
+    <t>/assignments/decesion_trees/decision_trees.Rmd</t>
+  </si>
+  <si>
+    <t>/assignments/bagging_and_random_forests/bagging_and_random_forests.Rmd</t>
+  </si>
+  <si>
+    <t>/assignments/support_vector_machines/support_vector_machines.Rmd</t>
+  </si>
+  <si>
+    <t>/assignments/principal_component_analysis/principal_component_analysis.Rmd</t>
+  </si>
+  <si>
+    <t>/assignments/clustering/clustering.Rmd</t>
   </si>
 </sst>
 </file>
@@ -1143,19 +1143,19 @@
         <v>46265</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1175,19 +1175,19 @@
         <v>46272</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="I3" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1207,19 +1207,19 @@
         <v>46279</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="H4" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="I4" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1242,16 +1242,16 @@
         <v>7</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="H5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1274,10 +1274,10 @@
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1300,10 +1300,10 @@
         <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1326,10 +1326,10 @@
         <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1352,10 +1352,10 @@
         <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1378,10 +1378,10 @@
         <v>6</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1404,10 +1404,10 @@
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -1430,10 +1430,10 @@
         <v>5</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1453,7 +1453,7 @@
         <v>46342</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D14" s="4"/>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1487,10 +1487,10 @@
         <v>46356</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1513,7 +1513,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS382 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F48860-1C43-A540-BEB0-0D99543B70DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6AC804-732D-E844-AF1E-F10832B54321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="5100" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
+    <workbookView xWindow="1060" yWindow="8340" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>Week</t>
   </si>
@@ -207,6 +207,12 @@
   </si>
   <si>
     <t>/assignments/clustering/clustering.Rmd</t>
+  </si>
+  <si>
+    <t>06-Resampling_Methods</t>
+  </si>
+  <si>
+    <t>CTPCfYMrj2o</t>
   </si>
 </sst>
 </file>
@@ -1305,6 +1311,12 @@
       <c r="G7" t="s">
         <v>52</v>
       </c>
+      <c r="H7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS382 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6AC804-732D-E844-AF1E-F10832B54321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9FBED1-7DAE-2F49-8D45-5A0ECA5EEB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="8340" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Week</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>CTPCfYMrj2o</t>
+  </si>
+  <si>
+    <t>07-Trees</t>
   </si>
 </sst>
 </file>
@@ -1343,6 +1346,9 @@
       <c r="G8" t="s">
         <v>53</v>
       </c>
+      <c r="H8" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS382 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9FBED1-7DAE-2F49-8D45-5A0ECA5EEB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41892545-C141-6242-AE14-1F4BBB631424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="8340" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>Week</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Generative Models for Classification</t>
   </si>
   <si>
-    <t>Bagging and Random Forests</t>
-  </si>
-  <si>
     <t>Resampling Methods</t>
   </si>
   <si>
@@ -131,9 +128,6 @@
     <t>/modules/07-Tree_Models.html</t>
   </si>
   <si>
-    <t>/modules/08-Bagging_and_Random_Forests.html</t>
-  </si>
-  <si>
     <t>/modules/09-Support_Vector_Machines.html</t>
   </si>
   <si>
@@ -216,6 +210,18 @@
   </si>
   <si>
     <t>07-Trees</t>
+  </si>
+  <si>
+    <t>08-Ensemble_Methods</t>
+  </si>
+  <si>
+    <t>EB2s9mtSsnI</t>
+  </si>
+  <si>
+    <t>Ensemble Methods</t>
+  </si>
+  <si>
+    <t>/modules/08-Ensemble_Methods.html</t>
   </si>
 </sst>
 </file>
@@ -1115,25 +1121,25 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>17</v>
-      </c>
-      <c r="J1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -1152,19 +1158,19 @@
         <v>46265</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1184,19 +1190,19 @@
         <v>46272</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1216,19 +1222,19 @@
         <v>46279</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1251,16 +1257,16 @@
         <v>7</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1283,10 +1289,10 @@
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1306,19 +1312,19 @@
         <v>46300</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1338,16 +1344,16 @@
         <v>46307</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1367,13 +1373,19 @@
         <v>46314</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="G9" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1396,10 +1408,10 @@
         <v>6</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1422,10 +1434,10 @@
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -1448,10 +1460,10 @@
         <v>5</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1471,7 +1483,7 @@
         <v>46342</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1485,7 +1497,7 @@
       </c>
       <c r="D14" s="4"/>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1505,10 +1517,10 @@
         <v>46356</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1528,10 +1540,10 @@
         <v>46363</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
